--- a/medical_surveys_questionnaires/042_hair_loss_treatment_awareness_survey--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/042_hair_loss_treatment_awareness_survey--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>plan_to_treat_hair_loss</t>
+          <t>plan to treat hair loss</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>do_not_plan_to_treat_hair_loss</t>
+          <t>do not plan to treat hair loss</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>financial_constraints</t>
+          <t>financial constraints</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>lack_of_information</t>
+          <t>lack of information</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>personal_preferences</t>
+          <t>personal preferences</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>service_availability</t>
+          <t>service availability</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>social media</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>online_search</t>
+          <t>online search</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>very_aware</t>
+          <t>very aware</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>somewhat_aware</t>
+          <t>somewhat aware</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>not_aware</t>
+          <t>not aware</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>social media</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>online_search</t>
+          <t>online search</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>very_influential</t>
+          <t>very influential</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>somewhat_influential</t>
+          <t>somewhat influential</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>not_influential</t>
+          <t>not influential</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>social media</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>online_search</t>
+          <t>online search</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>healthcare_professionals</t>
+          <t>healthcare professionals</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>very_aware</t>
+          <t>very aware</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>somewhat_aware</t>
+          <t>somewhat aware</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>not_aware</t>
+          <t>not aware</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>very_important</t>
+          <t>very important</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>somewhat_important</t>
+          <t>somewhat important</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>not_important</t>
+          <t>not important</t>
         </is>
       </c>
     </row>
